--- a/resources/templates/standard/L2300-06.xlsx
+++ b/resources/templates/standard/L2300-06.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>0000치구  관리 대장</t>
   </si>
@@ -709,9 +712,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -720,16 +725,16 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -762,35 +767,35 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="12"/>
       <c r="J3" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="7"/>
@@ -910,7 +915,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
